--- a/ruler_chung/tuongtachoatchat.xlsx
+++ b/ruler_chung/tuongtachoatchat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\check_3176_NEW_13072026\danh_muc_cong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\check_3176_FULL_TEST\ruler_chung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7854C37B-F6F0-4F54-8043-5F55E4C3B2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB451DE-3642-4F83-A742-45D02BD794D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>MA_HOAT_CHAT</t>
   </si>
@@ -33,16 +33,7 @@
     <t>TEN_HOAT_CHAT</t>
   </si>
   <si>
-    <t>40.594;40.598</t>
-  </si>
-  <si>
     <t>GHI_CHU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bệnh nhân  sẽ mẩn ngữa </t>
-  </si>
-  <si>
-    <t>40.593</t>
   </si>
 </sst>
 </file>
@@ -361,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
@@ -378,18 +369,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
